--- a/ig/main/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1139">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -564,7 +564,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>Orthoptie</t>
+    <t>Orthoptie : exploration et rééducation de la fonction visuelle</t>
   </si>
   <si>
     <t>110</t>
@@ -3360,13 +3360,13 @@
     <t>625</t>
   </si>
   <si>
-    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+    <t>Orthoptie orientation neurovisuelle adulte (pathologies neurologiques, maladies neurodégénératives)</t>
   </si>
   <si>
     <t>626</t>
   </si>
   <si>
-    <t>Orthoptie orientation basse vision</t>
+    <t>Orthoptie Basse Vision adulte</t>
   </si>
   <si>
     <t>627</t>
@@ -3397,6 +3397,30 @@
   </si>
   <si>
     <t>Prise en charge et coordination de plaies et cicatrisations complexes</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>Médecine nucléaire - Diagnostic</t>
+  </si>
+  <si>
+    <t>633</t>
+  </si>
+  <si>
+    <t>Médecine nucléaire - Thérapie</t>
+  </si>
+  <si>
+    <t>634</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation neurovisuelle enfant</t>
+  </si>
+  <si>
+    <t>635</t>
+  </si>
+  <si>
+    <t>Orthoptie Basse Vision enfant</t>
   </si>
   <si>
     <t/>
@@ -3667,7 +3691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B553"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -8087,15 +8111,47 @@
         <v>1128</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="s" s="2">
+        <v>1132</v>
+      </c>
+      <c r="B554" t="s" s="2">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="B555" t="s" s="2">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="s" s="2">
+        <v>1136</v>
+      </c>
+      <c r="B556" t="s" s="2">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="s" s="2">
+        <v>1137</v>
+      </c>
+      <c r="B557" t="s" s="2">
+        <v>1138</v>
       </c>
     </row>
   </sheetData>
